--- a/research/traditional_assets/database/data/canada/canada_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_auto_truck.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-12.92892156862745</v>
+        <v>-7.12748643761302</v>
       </c>
       <c r="H2">
-        <v>-31.98529411764706</v>
+        <v>-11.18083182640145</v>
       </c>
       <c r="I2">
-        <v>-64.30820500373979</v>
+        <v>-15.71373887559192</v>
       </c>
       <c r="J2">
-        <v>-64.30820500373979</v>
+        <v>-15.71373887559192</v>
       </c>
       <c r="K2">
-        <v>-66.08799999999999</v>
+        <v>-81.673</v>
       </c>
       <c r="L2">
-        <v>-80.99019607843137</v>
+        <v>-14.76907775768535</v>
       </c>
       <c r="M2">
-        <v>0.205</v>
+        <v>0.104</v>
       </c>
       <c r="N2">
-        <v>0.00070446735395189</v>
+        <v>0.001161103047895501</v>
       </c>
       <c r="O2">
-        <v>-0.003101924706452003</v>
+        <v>-0.001273370636562879</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,64 +624,73 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.205</v>
+        <v>0.104</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>228.8</v>
+        <v>155.014</v>
       </c>
       <c r="V2">
-        <v>0.7862542955326461</v>
+        <v>1.730646421793011</v>
+      </c>
+      <c r="W2">
+        <v>-15</v>
       </c>
       <c r="X2">
-        <v>0.05974578884440969</v>
+        <v>0.1004957585936894</v>
+      </c>
+      <c r="Y2">
+        <v>-15.10049575859369</v>
       </c>
       <c r="Z2">
-        <v>0.1195170734206236</v>
+        <v>0.1142919029720227</v>
       </c>
       <c r="AB2">
-        <v>0.05950985526675726</v>
+        <v>0.1003174136950706</v>
       </c>
       <c r="AD2">
-        <v>2.09</v>
+        <v>17.946</v>
       </c>
       <c r="AE2">
-        <v>1.342476415258274</v>
+        <v>25.84487991011645</v>
       </c>
       <c r="AF2">
-        <v>3.432476415258274</v>
+        <v>43.79087991011645</v>
       </c>
       <c r="AG2">
-        <v>-225.3675235847417</v>
+        <v>-111.2231200898836</v>
       </c>
       <c r="AH2">
-        <v>0.01165794092095064</v>
+        <v>0.3283637595944999</v>
       </c>
       <c r="AI2">
-        <v>0.01355464537506475</v>
+        <v>0.1789838366260036</v>
       </c>
       <c r="AJ2">
-        <v>-3.433780589945076</v>
+        <v>5.136586303876247</v>
       </c>
       <c r="AK2">
-        <v>-9.224096639012737</v>
+        <v>-1.240638807340251</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.713</v>
       </c>
       <c r="AM2">
-        <v>-0.283</v>
+        <v>-0.5280000000000001</v>
       </c>
       <c r="AN2">
-        <v>-0.04269314049924419</v>
+        <v>-0.231322505800464</v>
+      </c>
+      <c r="AO2">
+        <v>-118.4824684431978</v>
       </c>
       <c r="AP2">
-        <v>4.603659018358903</v>
+        <v>1.433657129284398</v>
       </c>
       <c r="AQ2">
-        <v>187.113074204947</v>
+        <v>159.9962121212121</v>
       </c>
     </row>
     <row r="3">
@@ -701,31 +710,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-13.11274509803922</v>
+        <v>-6.455696202531644</v>
       </c>
       <c r="H3">
-        <v>-31.98529411764706</v>
+        <v>-10.36166365280289</v>
       </c>
       <c r="I3">
-        <v>-63.75305794491625</v>
+        <v>-14.8497244090458</v>
       </c>
       <c r="J3">
-        <v>-63.75305794491625</v>
+        <v>-14.8497244090458</v>
       </c>
       <c r="K3">
-        <v>-65.59999999999999</v>
+        <v>-76.5</v>
       </c>
       <c r="L3">
-        <v>-80.3921568627451</v>
+        <v>-13.83363471971067</v>
       </c>
       <c r="M3">
-        <v>0.205</v>
+        <v>0.104</v>
       </c>
       <c r="N3">
-        <v>0.0007680779318096666</v>
+        <v>0.001448467966573816</v>
       </c>
       <c r="O3">
-        <v>-0.003125</v>
+        <v>-0.001359477124183007</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -737,76 +746,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.205</v>
+        <v>0.104</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>228.8</v>
+        <v>153.9</v>
       </c>
       <c r="V3">
-        <v>0.8572499063319596</v>
+        <v>2.143454038997215</v>
       </c>
       <c r="W3">
-        <v>-0.8118811881188118</v>
+        <v>-0.3062449959967974</v>
       </c>
       <c r="X3">
-        <v>0.05995580324980572</v>
+        <v>0.1284739724694503</v>
       </c>
       <c r="Y3">
-        <v>-0.8718369913686176</v>
+        <v>-0.4347189684662477</v>
       </c>
       <c r="Z3">
-        <v>0.1195170734206236</v>
+        <v>0.1142919029720227</v>
       </c>
       <c r="AA3">
-        <v>-7.619578907191827</v>
+        <v>-1.69720326131994</v>
       </c>
       <c r="AB3">
-        <v>0.05948393609450085</v>
+        <v>0.09545128722430918</v>
       </c>
       <c r="AC3">
-        <v>-7.679062843286328</v>
+        <v>-1.792654548544249</v>
       </c>
       <c r="AD3">
-        <v>2.09</v>
+        <v>17.9</v>
       </c>
       <c r="AE3">
-        <v>1.342476415258274</v>
+        <v>25.84487991011645</v>
       </c>
       <c r="AF3">
-        <v>3.432476415258274</v>
+        <v>43.74487991011645</v>
       </c>
       <c r="AG3">
-        <v>-225.3675235847417</v>
+        <v>-110.1551200898836</v>
       </c>
       <c r="AH3">
-        <v>0.01269724030488161</v>
+        <v>0.3785964375413782</v>
       </c>
       <c r="AI3">
-        <v>0.01355464537506475</v>
+        <v>0.1890077668907826</v>
       </c>
       <c r="AJ3">
-        <v>-5.426296311624367</v>
+        <v>2.871979538370362</v>
       </c>
       <c r="AK3">
-        <v>-9.224096639012737</v>
+        <v>-1.420533763384071</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.713</v>
       </c>
       <c r="AM3">
-        <v>-0.283</v>
+        <v>-0.3770000000000001</v>
       </c>
       <c r="AN3">
-        <v>-0.04269314049924419</v>
+        <v>-0.245037645448323</v>
+      </c>
+      <c r="AO3">
+        <v>-111.781206171108</v>
       </c>
       <c r="AP3">
-        <v>4.603659018358903</v>
+        <v>1.507941411223594</v>
       </c>
       <c r="AQ3">
-        <v>185.5123674911661</v>
+        <v>211.4058355437665</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +838,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-0.488</v>
+        <v>-4.53</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -850,16 +862,22 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.2039755351681957</v>
+      </c>
+      <c r="W4">
+        <v>-15</v>
       </c>
       <c r="X4">
-        <v>0.05953577443901365</v>
+        <v>0.1003493136749456</v>
+      </c>
+      <c r="Y4">
+        <v>-15.10034931367495</v>
       </c>
       <c r="AB4">
-        <v>0.05953577443901365</v>
+        <v>0.1003493136749456</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -871,19 +889,117 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>-0.667</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>-0.2562427967729543</v>
+      </c>
+      <c r="AK4">
+        <v>-111.1666666666666</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AP4">
+        <v>0.1472406181015453</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EV Technology Group Ltd. (NEOE:EVTG)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Auto &amp; Truck</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>-0.643</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.447</v>
+      </c>
+      <c r="V5">
+        <v>0.03082758620689655</v>
+      </c>
+      <c r="X5">
+        <v>0.1004957585936894</v>
+      </c>
+      <c r="AB5">
+        <v>0.1003174136950706</v>
+      </c>
+      <c r="AD5">
+        <v>0.046</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0.046</v>
+      </c>
+      <c r="AG5">
+        <v>-0.401</v>
+      </c>
+      <c r="AH5">
+        <v>0.003162381410697099</v>
+      </c>
+      <c r="AI5">
+        <v>0.003666507253307827</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.02844173345627349</v>
+      </c>
+      <c r="AK5">
+        <v>-0.03314323497809737</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>-0.151</v>
+      </c>
+      <c r="AQ5">
+        <v>1.642384105960265</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_auto_truck.xlsx
@@ -587,32 +587,35 @@
           <t>Auto &amp; Truck</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.439</v>
+      </c>
       <c r="G2">
-        <v>-7.12748643761302</v>
+        <v>-28.90058823529412</v>
       </c>
       <c r="H2">
-        <v>-11.18083182640145</v>
+        <v>-33.11176470588235</v>
       </c>
       <c r="I2">
-        <v>-15.71373887559192</v>
+        <v>-25.90294117647059</v>
       </c>
       <c r="J2">
-        <v>-15.71373887559192</v>
+        <v>-25.90294117647059</v>
       </c>
       <c r="K2">
-        <v>-81.673</v>
+        <v>-128.47</v>
       </c>
       <c r="L2">
-        <v>-14.76907775768535</v>
+        <v>-37.78529411764706</v>
       </c>
       <c r="M2">
-        <v>0.104</v>
+        <v>0.065</v>
       </c>
       <c r="N2">
-        <v>0.001161103047895501</v>
+        <v>0.001585133882846413</v>
       </c>
       <c r="O2">
-        <v>-0.001273370636562879</v>
+        <v>-0.0005059546975947693</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,73 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.104</v>
+        <v>0.065</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>155.014</v>
+        <v>73.529</v>
       </c>
       <c r="V2">
-        <v>1.730646421793011</v>
+        <v>1.793127834950983</v>
       </c>
       <c r="W2">
-        <v>-15</v>
+        <v>-1.312</v>
       </c>
       <c r="X2">
-        <v>0.1004957585936894</v>
+        <v>0.1001939361835475</v>
       </c>
       <c r="Y2">
-        <v>-15.10049575859369</v>
+        <v>-1.412193936183547</v>
       </c>
       <c r="Z2">
-        <v>0.1142919029720227</v>
+        <v>0.05328735992477079</v>
+      </c>
+      <c r="AA2">
+        <v>-1.514506769825919</v>
       </c>
       <c r="AB2">
-        <v>0.1003174136950706</v>
+        <v>0.08196976955064622</v>
+      </c>
+      <c r="AC2">
+        <v>-1.596476539376565</v>
       </c>
       <c r="AD2">
-        <v>17.946</v>
+        <v>18.51</v>
       </c>
       <c r="AE2">
-        <v>25.84487991011645</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>43.79087991011645</v>
+        <v>18.51</v>
       </c>
       <c r="AG2">
-        <v>-111.2231200898836</v>
+        <v>-55.01899999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3283637595944999</v>
+        <v>0.3110088043551314</v>
       </c>
       <c r="AI2">
-        <v>0.1789838366260036</v>
+        <v>0.1802916224297973</v>
       </c>
       <c r="AJ2">
-        <v>5.136586303876247</v>
+        <v>3.926282737458076</v>
       </c>
       <c r="AK2">
-        <v>-1.240638807340251</v>
+        <v>-1.888221566339486</v>
       </c>
       <c r="AL2">
-        <v>0.713</v>
+        <v>0.131</v>
       </c>
       <c r="AM2">
-        <v>-0.5280000000000001</v>
+        <v>-5.329</v>
       </c>
       <c r="AN2">
-        <v>-0.231322505800464</v>
+        <v>-0.2189237137788291</v>
       </c>
       <c r="AO2">
-        <v>-118.4824684431978</v>
+        <v>-672.2900763358778</v>
       </c>
       <c r="AP2">
-        <v>1.433657129284398</v>
+        <v>0.6507273802483736</v>
       </c>
       <c r="AQ2">
-        <v>159.9962121212121</v>
+        <v>16.52655282416964</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Electrameccanica Vehicles Corp. (NasdaqCM:SOLO)</t>
+          <t>EV Technology Group Ltd. (NEOE:EVTG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,32 +718,17 @@
           <t>Auto &amp; Truck</t>
         </is>
       </c>
-      <c r="G3">
-        <v>-6.455696202531644</v>
-      </c>
-      <c r="H3">
-        <v>-10.36166365280289</v>
-      </c>
-      <c r="I3">
-        <v>-14.8497244090458</v>
-      </c>
-      <c r="J3">
-        <v>-14.8497244090458</v>
-      </c>
       <c r="K3">
-        <v>-76.5</v>
-      </c>
-      <c r="L3">
-        <v>-13.83363471971067</v>
+        <v>-16.4</v>
       </c>
       <c r="M3">
-        <v>0.104</v>
+        <v>0.047</v>
       </c>
       <c r="N3">
-        <v>0.001448467966573816</v>
+        <v>0.05642256902761104</v>
       </c>
       <c r="O3">
-        <v>-0.001359477124183007</v>
+        <v>-0.002865853658536586</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,79 +740,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.104</v>
+        <v>0.047</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>153.9</v>
+        <v>0.005</v>
       </c>
       <c r="V3">
-        <v>2.143454038997215</v>
+        <v>0.006002400960384154</v>
       </c>
       <c r="W3">
-        <v>-0.3062449959967974</v>
+        <v>-1.312</v>
       </c>
       <c r="X3">
-        <v>0.1284739724694503</v>
+        <v>0.1428104193261463</v>
       </c>
       <c r="Y3">
-        <v>-0.4347189684662477</v>
+        <v>-1.454810419326146</v>
       </c>
       <c r="Z3">
-        <v>0.1142919029720227</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-1.69720326131994</v>
+        <v>-0.6818745350855443</v>
       </c>
       <c r="AB3">
-        <v>0.09545128722430918</v>
+        <v>0.07811240391303638</v>
       </c>
       <c r="AC3">
-        <v>-1.792654548544249</v>
+        <v>-0.7599869389985807</v>
       </c>
       <c r="AD3">
-        <v>17.9</v>
+        <v>1.39</v>
       </c>
       <c r="AE3">
-        <v>25.84487991011645</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>43.74487991011645</v>
+        <v>1.39</v>
       </c>
       <c r="AG3">
-        <v>-110.1551200898836</v>
+        <v>1.385</v>
       </c>
       <c r="AH3">
-        <v>0.3785964375413782</v>
+        <v>0.6252811515969411</v>
       </c>
       <c r="AI3">
-        <v>0.1890077668907826</v>
+        <v>4.793103448275865</v>
       </c>
       <c r="AJ3">
-        <v>2.871979538370362</v>
+        <v>0.6244364292155095</v>
       </c>
       <c r="AK3">
-        <v>-1.420533763384071</v>
+        <v>4.859649122807019</v>
       </c>
       <c r="AL3">
-        <v>0.713</v>
+        <v>0.131</v>
       </c>
       <c r="AM3">
-        <v>-0.3770000000000001</v>
+        <v>-0.169</v>
       </c>
       <c r="AN3">
-        <v>-0.245037645448323</v>
+        <v>-0.1688942891859052</v>
       </c>
       <c r="AO3">
-        <v>-111.781206171108</v>
+        <v>-62.97709923664122</v>
       </c>
       <c r="AP3">
-        <v>1.507941411223594</v>
+        <v>-0.1682867557715674</v>
       </c>
       <c r="AQ3">
-        <v>211.4058355437665</v>
+        <v>48.81656804733728</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TUGA Innovations, Inc. (CNSX:TUGA)</t>
+          <t>Electrameccanica Vehicles Corp. (NasdaqCM:SOLO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,17 +831,35 @@
           <t>Auto &amp; Truck</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.439</v>
+      </c>
+      <c r="G4">
+        <v>-24.44117647058824</v>
+      </c>
+      <c r="H4">
+        <v>-28.5</v>
+      </c>
+      <c r="I4">
+        <v>-23.02941176470588</v>
+      </c>
+      <c r="J4">
+        <v>-23.02941176470588</v>
+      </c>
       <c r="K4">
-        <v>-4.53</v>
+        <v>-110</v>
+      </c>
+      <c r="L4">
+        <v>-32.35294117647059</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.018</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.00045</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0.0001636363636363636</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -859,61 +871,76 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.018</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>0.667</v>
+        <v>73.5</v>
       </c>
       <c r="V4">
-        <v>0.2039755351681957</v>
+        <v>1.8375</v>
       </c>
       <c r="W4">
-        <v>-15</v>
+        <v>-0.5860415556739478</v>
       </c>
       <c r="X4">
-        <v>0.1003493136749456</v>
+        <v>0.1001939361835475</v>
       </c>
       <c r="Y4">
-        <v>-15.10034931367495</v>
+        <v>-0.6862354918574952</v>
+      </c>
+      <c r="Z4">
+        <v>0.06576402321083173</v>
+      </c>
+      <c r="AA4">
+        <v>-1.514506769825919</v>
       </c>
       <c r="AB4">
-        <v>0.1003493136749456</v>
+        <v>0.08196976955064622</v>
+      </c>
+      <c r="AC4">
+        <v>-1.596476539376565</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="AG4">
-        <v>-0.667</v>
+        <v>-56.4</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.2994746059544658</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.1660194174757282</v>
       </c>
       <c r="AJ4">
-        <v>-0.2562427967729543</v>
+        <v>3.439024390243903</v>
       </c>
       <c r="AK4">
-        <v>-111.1666666666666</v>
+        <v>-1.91186440677966</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-5.16</v>
       </c>
       <c r="AN4">
-        <v>-0</v>
+        <v>-0.2286096256684492</v>
       </c>
       <c r="AP4">
-        <v>0.1472406181015453</v>
+        <v>0.7540106951871658</v>
+      </c>
+      <c r="AQ4">
+        <v>15.17441860465116</v>
       </c>
     </row>
     <row r="5">
@@ -924,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EV Technology Group Ltd. (NEOE:EVTG)</t>
+          <t>TUGA Innovations, Inc. (CNSX:TUGA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -933,7 +960,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-0.643</v>
+        <v>-2.07</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -957,49 +984,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.447</v>
+        <v>0.024</v>
       </c>
       <c r="V5">
-        <v>0.03082758620689655</v>
+        <v>0.138728323699422</v>
+      </c>
+      <c r="W5">
+        <v>-3.075780089153046</v>
       </c>
       <c r="X5">
-        <v>0.1004957585936894</v>
+        <v>0.0894848370167913</v>
+      </c>
+      <c r="Y5">
+        <v>-3.165264926169837</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>-253.3333333333331</v>
       </c>
       <c r="AB5">
-        <v>0.1003174136950706</v>
+        <v>0.08428849535702018</v>
+      </c>
+      <c r="AC5">
+        <v>-253.4176218286901</v>
       </c>
       <c r="AD5">
-        <v>0.046</v>
+        <v>0.02</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.046</v>
+        <v>0.02</v>
       </c>
       <c r="AG5">
-        <v>-0.401</v>
+        <v>-0.004</v>
       </c>
       <c r="AH5">
-        <v>0.003162381410697099</v>
+        <v>0.1036269430051814</v>
       </c>
       <c r="AI5">
-        <v>0.003666507253307827</v>
+        <v>-0.03210272873194222</v>
       </c>
       <c r="AJ5">
-        <v>-0.02844173345627349</v>
+        <v>-0.02366863905325444</v>
       </c>
       <c r="AK5">
-        <v>-0.03314323497809737</v>
+        <v>0.006182380216383307</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.151</v>
-      </c>
-      <c r="AQ5">
-        <v>1.642384105960265</v>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>-0.0131578947368421</v>
+      </c>
+      <c r="AP5">
+        <v>0.002631578947368421</v>
       </c>
     </row>
   </sheetData>
